--- a/SystemCode/services/recommender-service/eval/User_Evaluation_Metrics/UserEvaluationMetrics.xlsx
+++ b/SystemCode/services/recommender-service/eval/User_Evaluation_Metrics/UserEvaluationMetrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Downloads\User_Evaluation_Metrics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\fashion-recommender\SystemCode\services\recommender-service\eval\User_Evaluation_Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C859847C-A409-433F-88F3-EB75C7FD43AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1899A02A-D15D-4889-92FF-C6DC1B2E3347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D7F1A06-760D-46D9-AC64-FD1B47CA86D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8D7F1A06-760D-46D9-AC64-FD1B47CA86D6}"/>
   </bookViews>
   <sheets>
     <sheet name="KG" sheetId="1" r:id="rId1"/>
@@ -331,12 +331,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -366,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -376,6 +382,7 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2193,7 +2200,7 @@
       <c r="C2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2207,7 +2214,7 @@
       <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2218,7 +2225,7 @@
       <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -2232,7 +2239,7 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2249,7 +2256,7 @@
       <c r="C6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2260,7 +2267,7 @@
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2274,7 +2281,7 @@
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2291,7 +2298,7 @@
       <c r="C9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2305,7 +2312,7 @@
       <c r="C10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2319,7 +2326,7 @@
       <c r="C11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2330,7 +2337,7 @@
       <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2344,7 +2351,7 @@
       <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
